--- a/excel-rad/sifrarnik-paket/SPC_master_atributivne.xlsx
+++ b/excel-rad/sifrarnik-paket/SPC_master_atributivne.xlsx
@@ -9,9 +9,13 @@
     <sheet name="greske_katalog" sheetId="4" r:id="rId4"/>
     <sheet name="katalog_gresaka_vozilo" sheetId="5" r:id="rId5"/>
     <sheet name="delovi" sheetId="6" r:id="rId6"/>
-    <sheet name="radnici" sheetId="7" r:id="rId7"/>
-    <sheet name="radni_nalozi" sheetId="8" r:id="rId8"/>
-    <sheet name="kontrolna_lista_stavke" sheetId="9" r:id="rId9"/>
+    <sheet name="ciljevi" sheetId="7" r:id="rId7"/>
+    <sheet name="radnici" sheetId="8" r:id="rId8"/>
+    <sheet name="radni_nalozi" sheetId="9" r:id="rId9"/>
+    <sheet name="kupci" sheetId="10" r:id="rId10"/>
+    <sheet name="kontrolna_lista_stavke" sheetId="11" r:id="rId11"/>
+    <sheet name="merila" sheetId="12" r:id="rId12"/>
+    <sheet name="kalibracije" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -425,7 +429,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -442,7 +446,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -459,7 +463,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -476,7 +480,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
       <c r="B5" t="str">
@@ -493,7 +497,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
       <c r="B6" t="str">
@@ -510,14 +514,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
       <c r="B7" t="str">
         <v>Preseraj</v>
       </c>
       <c r="C7" t="str">
-        <v xml:space="preserve">Oblikovanje </v>
+        <v>Oblikovanje</v>
       </c>
       <c r="D7" t="str">
         <v>Savijanje</v>
@@ -527,14 +531,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
       <c r="B8" t="str">
         <v>Preseraj</v>
       </c>
       <c r="C8" t="str">
-        <v xml:space="preserve">Oblikovanje </v>
+        <v>Oblikovanje</v>
       </c>
       <c r="D8" t="str">
         <v>Rezanje</v>
@@ -544,7 +548,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
       <c r="B9" t="str">
@@ -561,7 +565,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="str">
         <v>9</v>
       </c>
       <c r="B10" t="str">
@@ -578,7 +582,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="str">
         <v>10</v>
       </c>
       <c r="B11" t="str">
@@ -595,7 +599,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="str">
         <v>11</v>
       </c>
       <c r="B12" t="str">
@@ -612,7 +616,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="str">
         <v>12</v>
       </c>
       <c r="B13" t="str">
@@ -629,7 +633,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="str">
         <v>13</v>
       </c>
       <c r="B14" t="str">
@@ -646,7 +650,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" t="str">
         <v>14</v>
       </c>
       <c r="B15" t="str">
@@ -663,7 +667,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="str">
         <v>15</v>
       </c>
       <c r="B16" t="str">
@@ -680,7 +684,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" t="str">
         <v>16</v>
       </c>
       <c r="B17" t="str">
@@ -697,7 +701,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
+      <c r="A18" t="str">
         <v>17</v>
       </c>
       <c r="B18" t="str">
@@ -714,7 +718,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" t="str">
         <v>18</v>
       </c>
       <c r="B19" t="str">
@@ -731,7 +735,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
+      <c r="A20" t="str">
         <v>19</v>
       </c>
       <c r="B20" t="str">
@@ -748,7 +752,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" t="str">
         <v>20</v>
       </c>
       <c r="B21" t="str">
@@ -765,7 +769,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
+      <c r="A22" t="str">
         <v>21</v>
       </c>
       <c r="B22" t="str">
@@ -782,7 +786,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
+      <c r="A23" t="str">
         <v>22</v>
       </c>
       <c r="B23" t="str">
@@ -799,7 +803,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
+      <c r="A24" t="str">
         <v>23</v>
       </c>
       <c r="B24" t="str">
@@ -816,7 +820,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
+      <c r="A25" t="str">
         <v>24</v>
       </c>
       <c r="B25" t="str">
@@ -833,7 +837,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
+      <c r="A26" t="str">
         <v>25</v>
       </c>
       <c r="B26" t="str">
@@ -850,7 +854,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
+      <c r="A27" t="str">
         <v>26</v>
       </c>
       <c r="B27" t="str">
@@ -867,7 +871,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
+      <c r="A28" t="str">
         <v>27</v>
       </c>
       <c r="B28" t="str">
@@ -884,7 +888,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
+      <c r="A29" t="str">
         <v>28</v>
       </c>
       <c r="B29" t="str">
@@ -901,7 +905,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" t="str">
         <v>29</v>
       </c>
       <c r="B30" t="str">
@@ -918,7 +922,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" t="str">
         <v>30</v>
       </c>
       <c r="B31" t="str">
@@ -935,7 +939,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" t="str">
         <v>31</v>
       </c>
       <c r="B32" t="str">
@@ -952,7 +956,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" t="str">
         <v>32</v>
       </c>
       <c r="B33" t="str">
@@ -969,7 +973,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" t="str">
         <v>33</v>
       </c>
       <c r="B34" t="str">
@@ -986,7 +990,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" t="str">
         <v>34</v>
       </c>
       <c r="B35" t="str">
@@ -1003,7 +1007,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="str">
         <v>35</v>
       </c>
       <c r="B36" t="str">
@@ -1020,7 +1024,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" t="str">
         <v>36</v>
       </c>
       <c r="B37" t="str">
@@ -1037,7 +1041,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="str">
         <v>37</v>
       </c>
       <c r="B38" t="str">
@@ -1054,7 +1058,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" t="str">
         <v>38</v>
       </c>
       <c r="B39" t="str">
@@ -1071,7 +1075,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="str">
         <v>39</v>
       </c>
       <c r="B40" t="str">
@@ -1088,7 +1092,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" t="str">
         <v>40</v>
       </c>
       <c r="B41" t="str">
@@ -1105,7 +1109,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
+      <c r="A42" t="str">
         <v>41</v>
       </c>
       <c r="B42" t="str">
@@ -1122,7 +1126,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
+      <c r="A43" t="str">
         <v>42</v>
       </c>
       <c r="B43" t="str">
@@ -1139,7 +1143,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
+      <c r="A44" t="str">
         <v>43</v>
       </c>
       <c r="B44" t="str">
@@ -1156,7 +1160,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
+      <c r="A45" t="str">
         <v>44</v>
       </c>
       <c r="B45" t="str">
@@ -1173,7 +1177,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
+      <c r="A46" t="str">
         <v>45</v>
       </c>
       <c r="B46" t="str">
@@ -1190,7 +1194,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
+      <c r="A47" t="str">
         <v>46</v>
       </c>
       <c r="B47" t="str">
@@ -1207,7 +1211,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" t="str">
         <v>47</v>
       </c>
       <c r="B48" t="str">
@@ -1224,7 +1228,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
+      <c r="A49" t="str">
         <v>48</v>
       </c>
       <c r="B49" t="str">
@@ -1241,7 +1245,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" t="str">
         <v>49</v>
       </c>
       <c r="B50" t="str">
@@ -1258,7 +1262,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
+      <c r="A51" t="str">
         <v>50</v>
       </c>
       <c r="B51" t="str">
@@ -1271,11 +1275,11 @@
         <v>Test vodonepropustivosti</v>
       </c>
       <c r="E51" t="str">
-        <v xml:space="preserve">Curenje tečnosti </v>
+        <v>Curenje tečnosti</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
+      <c r="A52" t="str">
         <v>51</v>
       </c>
       <c r="B52" t="str">
@@ -1292,7 +1296,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
+      <c r="A53" t="str">
         <v>52</v>
       </c>
       <c r="B53" t="str">
@@ -1309,7 +1313,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
+      <c r="A54" t="str">
         <v>53</v>
       </c>
       <c r="B54" t="str">
@@ -1326,7 +1330,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
+      <c r="A55" t="str">
         <v>54</v>
       </c>
       <c r="B55" t="str">
@@ -1343,7 +1347,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
+      <c r="A56" t="str">
         <v>55</v>
       </c>
       <c r="B56" t="str">
@@ -1360,7 +1364,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
+      <c r="A57" t="str">
         <v>56</v>
       </c>
       <c r="B57" t="str">
@@ -1377,7 +1381,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
+      <c r="A58" t="str">
         <v>57</v>
       </c>
       <c r="B58" t="str">
@@ -1394,7 +1398,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59">
+      <c r="A59" t="str">
         <v>58</v>
       </c>
       <c r="B59" t="str">
@@ -1411,7 +1415,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60">
+      <c r="A60" t="str">
         <v>59</v>
       </c>
       <c r="B60" t="str">
@@ -1428,7 +1432,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61">
+      <c r="A61" t="str">
         <v>60</v>
       </c>
       <c r="B61" t="str">
@@ -1447,6 +1451,503 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E61"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>naziv</v>
+      </c>
+      <c r="C1" t="str">
+        <v>aktivan</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Auto Industrija d.o.o.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>OEM Partner GmbH</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Lokalni servis</v>
+      </c>
+      <c r="C4" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>kategorija</v>
+      </c>
+      <c r="C1" t="str">
+        <v>stavka</v>
+      </c>
+      <c r="D1" t="str">
+        <v>redosled</v>
+      </c>
+      <c r="E1" t="str">
+        <v>aktivna</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>BEZBEDNOST</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Proverena lična zaštitna oprema (rukavice</v>
+      </c>
+      <c r="D2" t="str">
+        <v>naočari</v>
+      </c>
+      <c r="E2" t="str">
+        <v>obuća)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BEZBEDNOST</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Radno mesto je čisto i bez prepreka</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>OPREMA</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Mašina/alat je ispravan i spreman za rad</v>
+      </c>
+      <c r="D4" t="str">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>OPREMA</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Merila su dostupna i kalibrisana</v>
+      </c>
+      <c r="D5" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>DOKUMENTACIJA</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Radni nalog i crtež dela su dostupni</v>
+      </c>
+      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>DOKUMENTACIJA</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SOP / uputstvo za kontrolu je pročitano</v>
+      </c>
+      <c r="D7" t="str">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>MATERIJAL</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Materijal i delovi odgovaraju radnom nalogu</v>
+      </c>
+      <c r="D8" t="str">
+        <v>7</v>
+      </c>
+      <c r="E8" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>KVALITET</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Prethodna smena ostavila napomenu — provereno</v>
+      </c>
+      <c r="D9" t="str">
+        <v>8</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DA</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>naziv merila</v>
+      </c>
+      <c r="C1" t="str">
+        <v>serijski br.</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tip</v>
+      </c>
+      <c r="E1" t="str">
+        <v>lokacija</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opseg</v>
+      </c>
+      <c r="G1" t="str">
+        <v>datum kal.</v>
+      </c>
+      <c r="H1" t="str">
+        <v>sledeca kal.</v>
+      </c>
+      <c r="I1" t="str">
+        <v>izvrsio</v>
+      </c>
+      <c r="J1" t="str">
+        <v>cert br.</v>
+      </c>
+      <c r="K1" t="str">
+        <v>rezultat</v>
+      </c>
+      <c r="L1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Mikrometar 0-25mm</v>
+      </c>
+      <c r="C2" t="str">
+        <v>MK-001</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Mikrometar</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Linija Karoserija</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0-25mm</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2024-01-05</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2025-01-05</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Lab Kalibracija</v>
+      </c>
+      <c r="J2" t="str">
+        <v>CAL-2024-001</v>
+      </c>
+      <c r="K2" t="str">
+        <v>prolaz</v>
+      </c>
+      <c r="L2" t="str">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Pomicno merilo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>POM-002</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Pomicno</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Preseraj</v>
+      </c>
+      <c r="F3" t="str">
+        <v>0-150mm</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2023-12-15</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2024-12-15</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Lab Kalibracija</v>
+      </c>
+      <c r="J3" t="str">
+        <v>CAL-2023-098</v>
+      </c>
+      <c r="K3" t="str">
+        <v>prolaz</v>
+      </c>
+      <c r="L3" t="str">
+        <v>USKORO 25d</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Cigra 0.01mm</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CIG-003</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Cigra</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Montaza</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0-10mm</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2023-06-01</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2024-06-01</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Interni</v>
+      </c>
+      <c r="J4" t="str">
+        <v>INT-2023-012</v>
+      </c>
+      <c r="K4" t="str">
+        <v>uslovni</v>
+      </c>
+      <c r="L4" t="str">
+        <v>ISTEKLO</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>merilo id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>datum kal.</v>
+      </c>
+      <c r="D1" t="str">
+        <v>sledeca kal.</v>
+      </c>
+      <c r="E1" t="str">
+        <v>izvrsio</v>
+      </c>
+      <c r="F1" t="str">
+        <v>cert br.</v>
+      </c>
+      <c r="G1" t="str">
+        <v>rezultat</v>
+      </c>
+      <c r="H1" t="str">
+        <v>napomena</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2024-01-05</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2025-01-05</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Lab Kalibracija</v>
+      </c>
+      <c r="F2" t="str">
+        <v>CAL-2024-001</v>
+      </c>
+      <c r="G2" t="str">
+        <v>prolaz</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2023-12-15</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2024-12-15</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Lab Kalibracija</v>
+      </c>
+      <c r="F3" t="str">
+        <v>CAL-2023-098</v>
+      </c>
+      <c r="G3" t="str">
+        <v>prolaz</v>
+      </c>
+      <c r="H3" t="str">
+        <v>USKORO 25d</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2023-06-01</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2024-06-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Interni</v>
+      </c>
+      <c r="F4" t="str">
+        <v>INT-2023-012</v>
+      </c>
+      <c r="G4" t="str">
+        <v>uslovni</v>
+      </c>
+      <c r="H4" t="str">
+        <v>ISTEKLO</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1467,7 +1968,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -1478,7 +1979,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -1489,7 +1990,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -1525,7 +2026,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -1539,7 +2040,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -1553,7 +2054,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -1575,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:F56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1593,9 +2094,12 @@
       <c r="E1" t="str">
         <v>opis</v>
       </c>
+      <c r="F1" t="str">
+        <v>pogon kod</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -1610,9 +2114,12 @@
       <c r="E2" t="str">
         <v>Otvor u zavarenom spoju</v>
       </c>
+      <c r="F2" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -1627,9 +2134,12 @@
       <c r="E3" t="str">
         <v>Nedostaje zavareni spoj</v>
       </c>
+      <c r="F3" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -1644,9 +2154,12 @@
       <c r="E4" t="str">
         <v>Nedovoljna cvrstoca</v>
       </c>
+      <c r="F4" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
       <c r="B5" t="str">
@@ -1661,9 +2174,12 @@
       <c r="E5" t="str">
         <v>Metalne kapljice oko vara</v>
       </c>
+      <c r="F5" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
       <c r="B6" t="str">
@@ -1678,9 +2194,12 @@
       <c r="E6" t="str">
         <v>Zazor veci od tolerancije</v>
       </c>
+      <c r="F6" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
       <c r="B7" t="str">
@@ -1695,9 +2214,12 @@
       <c r="E7" t="str">
         <v>Zazor manji od tolerancije</v>
       </c>
+      <c r="F7" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
       <c r="B8" t="str">
@@ -1712,9 +2234,12 @@
       <c r="E8" t="str">
         <v>Promenljiv zazor po obimu</v>
       </c>
+      <c r="F8" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
       <c r="B9" t="str">
@@ -1729,9 +2254,12 @@
       <c r="E9" t="str">
         <v>Mehanicka ostecenja</v>
       </c>
+      <c r="F9" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="str">
         <v>9</v>
       </c>
       <c r="B10" t="str">
@@ -1746,9 +2274,12 @@
       <c r="E10" t="str">
         <v>Deformacija povrsine</v>
       </c>
+      <c r="F10" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="str">
         <v>10</v>
       </c>
       <c r="B11" t="str">
@@ -1763,9 +2294,12 @@
       <c r="E11" t="str">
         <v>Korozija</v>
       </c>
+      <c r="F11" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="str">
         <v>11</v>
       </c>
       <c r="B12" t="str">
@@ -1780,9 +2314,12 @@
       <c r="E12" t="str">
         <v>Opsta deformacija oblika</v>
       </c>
+      <c r="F12" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="str">
         <v>12</v>
       </c>
       <c r="B13" t="str">
@@ -1797,9 +2334,12 @@
       <c r="E13" t="str">
         <v>Van dimenzionalne tolerancije</v>
       </c>
+      <c r="F13" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="str">
         <v>13</v>
       </c>
       <c r="B14" t="str">
@@ -1814,9 +2354,12 @@
       <c r="E14" t="str">
         <v>Van dimenzionalne tolerancije</v>
       </c>
+      <c r="F14" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" t="str">
         <v>14</v>
       </c>
       <c r="B15" t="str">
@@ -1831,9 +2374,12 @@
       <c r="E15" t="str">
         <v>Van dimenzionalne tolerancije</v>
       </c>
+      <c r="F15" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="str">
         <v>15</v>
       </c>
       <c r="B16" t="str">
@@ -1848,9 +2394,12 @@
       <c r="E16" t="str">
         <v>Neobradjena ivica</v>
       </c>
+      <c r="F16" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" t="str">
         <v>16</v>
       </c>
       <c r="B17" t="str">
@@ -1865,9 +2414,12 @@
       <c r="E17" t="str">
         <v>Vizuelno iskrivljenje</v>
       </c>
+      <c r="F17" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18">
+      <c r="A18" t="str">
         <v>17</v>
       </c>
       <c r="B18" t="str">
@@ -1882,9 +2434,12 @@
       <c r="E18" t="str">
         <v>Funkcionalna smetnja</v>
       </c>
+      <c r="F18" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" t="str">
         <v>18</v>
       </c>
       <c r="B19" t="str">
@@ -1899,9 +2454,12 @@
       <c r="E19" t="str">
         <v>Pogresno pozicioniranje</v>
       </c>
+      <c r="F19" t="str">
+        <v>C</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20">
+      <c r="A20" t="str">
         <v>19</v>
       </c>
       <c r="B20" t="str">
@@ -1916,9 +2474,12 @@
       <c r="E20" t="str">
         <v>Ugradjen krivi deo</v>
       </c>
+      <c r="F20" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" t="str">
         <v>20</v>
       </c>
       <c r="B21" t="str">
@@ -1933,9 +2494,12 @@
       <c r="E21" t="str">
         <v>Ispod propisane tvrdoce</v>
       </c>
+      <c r="F21" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22">
+      <c r="A22" t="str">
         <v>21</v>
       </c>
       <c r="B22" t="str">
@@ -1950,9 +2514,12 @@
       <c r="E22" t="str">
         <v>Iznad propisane tvrdoce</v>
       </c>
+      <c r="F22" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23">
+      <c r="A23" t="str">
         <v>22</v>
       </c>
       <c r="B23" t="str">
@@ -1967,9 +2534,12 @@
       <c r="E23" t="str">
         <v>Ostecena ambalaza</v>
       </c>
+      <c r="F23" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24">
+      <c r="A24" t="str">
         <v>23</v>
       </c>
       <c r="B24" t="str">
@@ -1984,9 +2554,12 @@
       <c r="E24" t="str">
         <v>Nedostaje komponenta</v>
       </c>
+      <c r="F24" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25">
+      <c r="A25" t="str">
         <v>24</v>
       </c>
       <c r="B25" t="str">
@@ -1998,9 +2571,15 @@
       <c r="D25" t="str">
         <v>Krivo</v>
       </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26">
+      <c r="A26" t="str">
         <v>25</v>
       </c>
       <c r="B26" t="str">
@@ -2012,9 +2591,15 @@
       <c r="D26" t="str">
         <v>Boja</v>
       </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27">
+      <c r="A27" t="str">
         <v>26</v>
       </c>
       <c r="B27" t="str">
@@ -2026,9 +2611,15 @@
       <c r="D27" t="str">
         <v>Nijanse</v>
       </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28">
+      <c r="A28" t="str">
         <v>27</v>
       </c>
       <c r="B28" t="str">
@@ -2040,9 +2631,15 @@
       <c r="D28" t="str">
         <v>Mrlje</v>
       </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29">
+      <c r="A29" t="str">
         <v>28</v>
       </c>
       <c r="B29" t="str">
@@ -2054,9 +2651,15 @@
       <c r="D29" t="str">
         <v>Etiketa</v>
       </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" t="str">
         <v>29</v>
       </c>
       <c r="B30" t="str">
@@ -2068,9 +2671,15 @@
       <c r="D30" t="str">
         <v>Ne radi</v>
       </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" t="str">
         <v>30</v>
       </c>
       <c r="B31" t="str">
@@ -2082,9 +2691,15 @@
       <c r="D31" t="str">
         <v>Blokira</v>
       </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" t="str">
         <v>31</v>
       </c>
       <c r="B32" t="str">
@@ -2096,9 +2711,15 @@
       <c r="D32" t="str">
         <v>Tesko radi</v>
       </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" t="str">
         <v>32</v>
       </c>
       <c r="B33" t="str">
@@ -2110,9 +2731,15 @@
       <c r="D33" t="str">
         <v>Zaglavljuje</v>
       </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" t="str">
         <v>33</v>
       </c>
       <c r="B34" t="str">
@@ -2124,9 +2751,15 @@
       <c r="D34" t="str">
         <v>Skripi</v>
       </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" t="str">
         <v>34</v>
       </c>
       <c r="B35" t="str">
@@ -2138,9 +2771,15 @@
       <c r="D35" t="str">
         <v>Nedostaje deo</v>
       </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="str">
         <v>35</v>
       </c>
       <c r="B36" t="str">
@@ -2152,9 +2791,15 @@
       <c r="D36" t="str">
         <v>Los polozaj</v>
       </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" t="str">
         <v>36</v>
       </c>
       <c r="B37" t="str">
@@ -2166,9 +2811,15 @@
       <c r="D37" t="str">
         <v>Pogresan deo</v>
       </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="str">
         <v>37</v>
       </c>
       <c r="B38" t="str">
@@ -2180,9 +2831,15 @@
       <c r="D38" t="str">
         <v>Krhko</v>
       </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" t="str">
         <v>38</v>
       </c>
       <c r="B39" t="str">
@@ -2194,9 +2851,15 @@
       <c r="D39" t="str">
         <v>Mekano</v>
       </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="str">
         <v>39</v>
       </c>
       <c r="B40" t="str">
@@ -2208,9 +2871,15 @@
       <c r="D40" t="str">
         <v>Tvrdo</v>
       </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" t="str">
         <v>40</v>
       </c>
       <c r="B41" t="str">
@@ -2222,9 +2891,15 @@
       <c r="D41" t="str">
         <v>Nehomogeno</v>
       </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42">
+      <c r="A42" t="str">
         <v>41</v>
       </c>
       <c r="B42" t="str">
@@ -2236,9 +2911,15 @@
       <c r="D42" t="str">
         <v>Pogresan</v>
       </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43">
+      <c r="A43" t="str">
         <v>42</v>
       </c>
       <c r="B43" t="str">
@@ -2250,9 +2931,15 @@
       <c r="D43" t="str">
         <v>Krhko</v>
       </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44">
+      <c r="A44" t="str">
         <v>43</v>
       </c>
       <c r="B44" t="str">
@@ -2264,9 +2951,15 @@
       <c r="D44" t="str">
         <v>Mekano</v>
       </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45">
+      <c r="A45" t="str">
         <v>44</v>
       </c>
       <c r="B45" t="str">
@@ -2278,9 +2971,15 @@
       <c r="D45" t="str">
         <v>Tvrdo</v>
       </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46">
+      <c r="A46" t="str">
         <v>45</v>
       </c>
       <c r="B46" t="str">
@@ -2292,9 +2991,15 @@
       <c r="D46" t="str">
         <v>Nehomogeno</v>
       </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47">
+      <c r="A47" t="str">
         <v>46</v>
       </c>
       <c r="B47" t="str">
@@ -2306,9 +3011,15 @@
       <c r="D47" t="str">
         <v>Osteceno</v>
       </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" t="str">
         <v>47</v>
       </c>
       <c r="B48" t="str">
@@ -2320,9 +3031,15 @@
       <c r="D48" t="str">
         <v>Pogresna etiketa</v>
       </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49">
+      <c r="A49" t="str">
         <v>48</v>
       </c>
       <c r="B49" t="str">
@@ -2334,9 +3051,15 @@
       <c r="D49" t="str">
         <v>Pogresno</v>
       </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" t="str">
         <v>49</v>
       </c>
       <c r="B50" t="str">
@@ -2348,9 +3071,15 @@
       <c r="D50" t="str">
         <v>Nedostaje deo</v>
       </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51">
+      <c r="A51" t="str">
         <v>50</v>
       </c>
       <c r="B51" t="str">
@@ -2362,9 +3091,15 @@
       <c r="D51" t="str">
         <v>Visak</v>
       </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52">
+      <c r="A52" t="str">
         <v>51</v>
       </c>
       <c r="B52" t="str">
@@ -2376,9 +3111,15 @@
       <c r="D52" t="str">
         <v>Pogresna sifra</v>
       </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53">
+      <c r="A53" t="str">
         <v>52</v>
       </c>
       <c r="B53" t="str">
@@ -2390,9 +3131,15 @@
       <c r="D53" t="str">
         <v>Nedostaje deo</v>
       </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54">
+      <c r="A54" t="str">
         <v>53</v>
       </c>
       <c r="B54" t="str">
@@ -2404,9 +3151,15 @@
       <c r="D54" t="str">
         <v>Necitko</v>
       </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55">
+      <c r="A55" t="str">
         <v>54</v>
       </c>
       <c r="B55" t="str">
@@ -2418,10 +3171,19 @@
       <c r="D55" t="str">
         <v>Pogresan dokument</v>
       </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>A</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56">
+      <c r="A56" t="str">
         <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
       </c>
       <c r="C56" t="str">
         <v>Ostalo</v>
@@ -2429,17 +3191,23 @@
       <c r="D56" t="str">
         <v>Ostalo</v>
       </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>A</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D352"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2457,7 +3225,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B2" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2471,7 +3239,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B3" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2485,7 +3253,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B4" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2494,12 +3262,12 @@
         <v>Prednji branik</v>
       </c>
       <c r="D4" t="str">
-        <v xml:space="preserve"> ogrebotine</v>
+        <v>ogrebotine</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B5" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2513,7 +3281,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B6" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2527,7 +3295,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B7" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2541,7 +3309,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B8" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2555,7 +3323,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B9" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2569,7 +3337,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B10" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2583,7 +3351,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B11" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2597,7 +3365,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B12" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2606,12 +3374,12 @@
         <v>Levo prednje krilo</v>
       </c>
       <c r="D12" t="str">
-        <v xml:space="preserve">Ogrebotine,, </v>
+        <v>Ogrebotine,,</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B13" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2620,12 +3388,12 @@
         <v>Levo prednje krilo</v>
       </c>
       <c r="D13" t="str">
-        <v xml:space="preserve"> ulubljenja (kontura)</v>
+        <v>ulubljenja (kontura)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B14" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2639,7 +3407,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B15" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2648,12 +3416,12 @@
         <v>Desno prednje krilo</v>
       </c>
       <c r="D15" t="str">
-        <v xml:space="preserve">Ogrebotine,, </v>
+        <v>Ogrebotine,,</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B16" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2662,12 +3430,12 @@
         <v>Desno prednje krilo</v>
       </c>
       <c r="D16" t="str">
-        <v xml:space="preserve"> ulubljenja (kontura)</v>
+        <v>ulubljenja (kontura)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B17" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2681,7 +3449,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B18" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2695,7 +3463,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B19" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2709,7 +3477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B20" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2723,7 +3491,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B21" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2737,7 +3505,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B22" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2751,7 +3519,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B23" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2765,7 +3533,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B24" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2779,7 +3547,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B25" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2793,7 +3561,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B26" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2807,7 +3575,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B27" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2821,7 +3589,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B28" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2835,7 +3603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B29" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2849,7 +3617,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B30" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2863,7 +3631,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B31" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2877,7 +3645,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B32" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2891,7 +3659,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B33" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2905,7 +3673,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B34" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2919,7 +3687,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B35" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2933,7 +3701,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B36" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2947,7 +3715,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B37" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2961,7 +3729,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B38" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2975,7 +3743,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B39" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -2989,7 +3757,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B40" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3003,7 +3771,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B41" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3017,7 +3785,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B42" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3031,7 +3799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B43" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3040,12 +3808,12 @@
         <v>Zadnji branik</v>
       </c>
       <c r="D43" t="str">
-        <v xml:space="preserve"> Loše poravnanje sa svetlima i krilima, i.</v>
+        <v>Loše poravnanje sa svetlima i krilima, i.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B44" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3059,7 +3827,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B45" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3068,12 +3836,12 @@
         <v>Zadnji branik</v>
       </c>
       <c r="D45" t="str">
-        <v xml:space="preserve"> labavi nosač</v>
+        <v>labavi nosač</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B46" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3082,12 +3850,12 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D46" t="str">
-        <v xml:space="preserve">Teško zatvaranje,  </v>
+        <v>Teško zatvaranje,</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B47" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3101,7 +3869,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B48" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3115,7 +3883,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B49" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3124,12 +3892,12 @@
         <v>Poklopac gepeka</v>
       </c>
       <c r="D49" t="str">
-        <v xml:space="preserve"> loše zaptivanje gume.</v>
+        <v>loše zaptivanje gume.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B50" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3143,7 +3911,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B51" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3157,7 +3925,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B52" t="str">
         <v>EKSTERIJER (Karoserija i Limarija)</v>
@@ -3171,7 +3939,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B53" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3185,7 +3953,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B54" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3199,7 +3967,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B55" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3208,12 +3976,12 @@
         <v>Vetrobran</v>
       </c>
       <c r="D55" t="str">
-        <v xml:space="preserve"> loša aplikacija lepka (curenje vode)</v>
+        <v>loša aplikacija lepka (curenje vode)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B56" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3227,7 +3995,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B57" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3236,12 +4004,12 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D57" t="str">
-        <v xml:space="preserve">Ogrebotine od podizanja/spuštanja, </v>
+        <v>Ogrebotine od podizanja/spuštanja,</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B58" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3250,12 +4018,12 @@
         <v>Bočna stakla</v>
       </c>
       <c r="D58" t="str">
-        <v xml:space="preserve"> zazor pri zatvaranju (prolaz vazduha),</v>
+        <v>zazor pri zatvaranju (prolaz vazduha),</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-KAROS-001</v>
       </c>
       <c r="B59" t="str">
         <v>STAKLENE POVRŠINE</v>
@@ -3269,777 +4037,777 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-MOTOR-001</v>
       </c>
       <c r="B60" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C60" t="str">
-        <v>Instrument tabla</v>
+        <v>Motorni prostor</v>
       </c>
       <c r="D60" t="str">
-        <v>Loš zazor na spojevima plastika,, , .</v>
+        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona),</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-MOTOR-001</v>
       </c>
       <c r="B61" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C61" t="str">
-        <v>Instrument tabla</v>
+        <v>Motorni prostor</v>
       </c>
       <c r="D61" t="str">
-        <v xml:space="preserve"> cvrčanje/škripa pri pritisku</v>
+        <v>labave obujmice creva</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-MOTOR-001</v>
       </c>
       <c r="B62" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C62" t="str">
-        <v>Instrument tabla</v>
+        <v>Motorni prostor</v>
       </c>
       <c r="D62" t="str">
-        <v>ogrebotine na mekim površinama</v>
+        <v>nepravilno rutirani kablovi</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-MOTOR-001</v>
       </c>
       <c r="B63" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C63" t="str">
-        <v>Instrument tabla</v>
+        <v>Motorni prostor</v>
       </c>
       <c r="D63" t="str">
-        <v>loše uklopljen vazdušni jastuk suvozača</v>
+        <v>nedostatak plastičnih poklopaca.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B64" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C64" t="str">
-        <v>Centralna konzola</v>
+        <v>Podvozje</v>
       </c>
       <c r="D64" t="str">
-        <v>Labavost naslona za ruku, , ,.</v>
+        <v>Curenje tečnosti na spojevima (menjač, karter), , ,</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B65" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C65" t="str">
-        <v>Centralna konzola</v>
+        <v>Podvozje</v>
       </c>
       <c r="D65" t="str">
-        <v>loš hod poklopaca/pregrada</v>
+        <v>labave zaštitne plastike (šuspleh)</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B66" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C66" t="str">
-        <v>Centralna konzola</v>
+        <v>Podvozje</v>
       </c>
       <c r="D66" t="str">
-        <v>ogrebotine na sjajnim (Piano black) površinama</v>
+        <v>korozija na spojevima</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B67" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C67" t="str">
-        <v>Centralna konzola</v>
+        <v>Podvozje</v>
       </c>
       <c r="D67" t="str">
-        <v xml:space="preserve"> labava ručica menjača</v>
+        <v>loše zategnuti elementi oslanjanja.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B68" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C68" t="str">
-        <v>Sedište vozača</v>
+        <v>Točkovi i gume</v>
       </c>
       <c r="D68" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Ogrebotine na alu-felnama, ,</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B69" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C69" t="str">
-        <v>Sedište vozača</v>
+        <v>Točkovi i gume</v>
       </c>
       <c r="D69" t="str">
-        <v xml:space="preserve"> naborana koža/tkanina</v>
+        <v>pogrešan smer rotacije gume,</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B70" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C70" t="str">
-        <v>Sedište vozača</v>
+        <v>Točkovi i gume</v>
       </c>
       <c r="D70" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>nedovoljan pritisak</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-TRANS-001</v>
       </c>
       <c r="B71" t="str">
-        <v>ENTERIJER (Kabina)</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C71" t="str">
-        <v>Sedište vozača</v>
+        <v>Točkovi i gume</v>
       </c>
       <c r="D71" t="str">
-        <v xml:space="preserve"> klimanje sedišta u šinama</v>
+        <v>nedostatak kapica na ventilima.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B72" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C72" t="str">
-        <v>Sedište suvozača</v>
+        <v>Instrument tabla</v>
       </c>
       <c r="D72" t="str">
-        <v>Oštećenje šavova,, .</v>
+        <v>Loš zazor na spojevima plastika,, , .</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B73" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C73" t="str">
-        <v>Sedište suvozača</v>
+        <v>Instrument tabla</v>
       </c>
       <c r="D73" t="str">
-        <v xml:space="preserve"> naborana koža/tkanina</v>
+        <v>cvrčanje/škripa pri pritisku</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B74" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C74" t="str">
-        <v>Sedište suvozača</v>
+        <v>Instrument tabla</v>
       </c>
       <c r="D74" t="str">
-        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+        <v>ogrebotine na mekim površinama</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B75" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C75" t="str">
-        <v>Sedište suvozača</v>
+        <v>Instrument tabla</v>
       </c>
       <c r="D75" t="str">
-        <v xml:space="preserve"> klimanje sedišta u šinama</v>
+        <v>loše uklopljen vazdušni jastuk suvozača</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B76" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C76" t="str">
-        <v>Zadnja sedišta</v>
+        <v>Centralna konzola</v>
       </c>
       <c r="D76" t="str">
-        <v xml:space="preserve"> Loše fiksiran donji deo klupe,  </v>
+        <v>Labavost naslona za ruku, , ,.</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B77" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C77" t="str">
-        <v>Zadnja sedišta</v>
+        <v>Centralna konzola</v>
       </c>
       <c r="D77" t="str">
-        <v>problem sa preklapanjem naslona,</v>
+        <v>loš hod poklopaca/pregrada</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B78" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C78" t="str">
-        <v>Zadnja sedišta</v>
+        <v>Centralna konzola</v>
       </c>
       <c r="D78" t="str">
-        <v>oštećenja ISOFIX priključaka.</v>
+        <v>ogrebotine na sjajnim (Piano black) površinama</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B79" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C79" t="str">
-        <v>Enterijer</v>
+        <v>Centralna konzola</v>
       </c>
       <c r="D79" t="str">
-        <v xml:space="preserve">Oštećenja tapacirunga krova (nebo),   </v>
+        <v>labava ručica menjača</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B80" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C80" t="str">
-        <v>Enterijer</v>
+        <v>Sedište vozača</v>
       </c>
       <c r="D80" t="str">
-        <v>ogrebotine na oblogama stubova (A, B, C),</v>
+        <v>Oštećenje šavova,, .</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B81" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C81" t="str">
-        <v>Enterijer</v>
+        <v>Sedište vozača</v>
       </c>
       <c r="D81" t="str">
-        <v>labavi rukohvati na krovu,</v>
+        <v>naborana koža/tkanina</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B82" t="str">
         <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C82" t="str">
-        <v>Enterijer</v>
+        <v>Sedište vozača</v>
       </c>
       <c r="D82" t="str">
-        <v>loše postavljeni tepisi/patosnice.</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B83" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C83" t="str">
-        <v>Prtljažni prostor</v>
+        <v>Sedište vozača</v>
       </c>
       <c r="D83" t="str">
-        <v xml:space="preserve">Labav pod gepeka, ,  </v>
+        <v>klimanje sedišta u šinama</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B84" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C84" t="str">
-        <v>Prtljažni prostor</v>
+        <v>Sedište suvozača</v>
       </c>
       <c r="D84" t="str">
-        <v>oštećenje bočnih tapacirunga</v>
+        <v>Oštećenje šavova,, .</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B85" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C85" t="str">
-        <v>Prtljažni prostor</v>
+        <v>Sedište suvozača</v>
       </c>
       <c r="D85" t="str">
-        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
+        <v>naborana koža/tkanina</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B86" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C86" t="str">
-        <v>Prtljažni prostor</v>
+        <v>Sedište suvozača</v>
       </c>
       <c r="D86" t="str">
-        <v>neispravno svetlo gepeka.</v>
+        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B87" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C87" t="str">
-        <v>Motorni prostor</v>
+        <v>Sedište suvozača</v>
       </c>
       <c r="D87" t="str">
-        <v xml:space="preserve">Nizak nivo tečnosti (ulje, rashladna, kočiona), </v>
+        <v>klimanje sedišta u šinama</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B88" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C88" t="str">
-        <v>Motorni prostor</v>
+        <v>Zadnja sedišta</v>
       </c>
       <c r="D88" t="str">
-        <v xml:space="preserve"> labave obujmice creva</v>
+        <v>Loše fiksiran donji deo klupe,</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B89" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C89" t="str">
-        <v>Motorni prostor</v>
+        <v>Zadnja sedišta</v>
       </c>
       <c r="D89" t="str">
-        <v>nepravilno rutirani kablovi</v>
+        <v>problem sa preklapanjem naslona,</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B90" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C90" t="str">
-        <v>Motorni prostor</v>
+        <v>Zadnja sedišta</v>
       </c>
       <c r="D90" t="str">
-        <v>nedostatak plastičnih poklopaca.</v>
+        <v>oštećenja ISOFIX priključaka.</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B91" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C91" t="str">
-        <v>Elektrika</v>
+        <v>Enterijer</v>
       </c>
       <c r="D91" t="str">
-        <v xml:space="preserve">Greška na instrument tabli, , , </v>
+        <v>Oštećenja tapacirunga krova (nebo),</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B92" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C92" t="str">
-        <v>Elektrika</v>
+        <v>Enterijer</v>
       </c>
       <c r="D92" t="str">
-        <v>nefunkcionalan USB/12V priključak</v>
+        <v>ogrebotine na oblogama stubova (A, B, C),</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B93" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C93" t="str">
-        <v>Elektrika</v>
+        <v>Enterijer</v>
       </c>
       <c r="D93" t="str">
-        <v>otkaz podizača prozora</v>
+        <v>labavi rukohvati na krovu,</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-INT-001</v>
       </c>
       <c r="B94" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>ENTERIJER (Kabina)</v>
       </c>
       <c r="C94" t="str">
-        <v>Elektrika</v>
+        <v>Enterijer</v>
       </c>
       <c r="D94" t="str">
-        <v>problem sa audio sistemom.</v>
+        <v>loše postavljeni tepisi/patosnice.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B95" t="str">
         <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C95" t="str">
-        <v>Funkcionalni test</v>
+        <v>Elektrika</v>
       </c>
       <c r="D95" t="str">
-        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
+        <v>Greška na instrument tabli, , ,</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B96" t="str">
         <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C96" t="str">
-        <v>Funkcionalni test</v>
+        <v>Elektrika</v>
       </c>
       <c r="D96" t="str">
-        <v>neispravna klima/grejanje</v>
+        <v>nefunkcionalan USB/12V priključak</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B97" t="str">
         <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C97" t="str">
-        <v>Funkcionalni test</v>
+        <v>Elektrika</v>
       </c>
       <c r="D97" t="str">
-        <v>otkaz električne ručne kočnice</v>
+        <v>otkaz podizača prozora</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B98" t="str">
         <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C98" t="str">
-        <v>Funkcionalni test</v>
+        <v>Elektrika</v>
       </c>
       <c r="D98" t="str">
-        <v>otkaz električne ručne kočnice</v>
+        <v>problem sa audio sistemom.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B99" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C99" t="str">
-        <v>Podvozje</v>
+        <v>Rasveta</v>
       </c>
       <c r="D99" t="str">
-        <v xml:space="preserve">Curenje tečnosti na spojevima (menjač, karter), , , </v>
+        <v>Kondenzacija (vlaga) unutar fara/stop svetla, , ,</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B100" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C100" t="str">
-        <v>Podvozje</v>
+        <v>Rasveta</v>
       </c>
       <c r="D100" t="str">
-        <v>labave zaštitne plastike (šuspleh)</v>
+        <v>nefunkcionalna LED traka</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B101" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C101" t="str">
-        <v>Podvozje</v>
+        <v>Rasveta</v>
       </c>
       <c r="D101" t="str">
-        <v>korozija na spojevima</v>
+        <v>loš intenzitet svetla</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B102" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C102" t="str">
-        <v>Podvozje</v>
+        <v>Rasveta</v>
       </c>
       <c r="D102" t="str">
-        <v>loše zategnuti elementi oslanjanja.</v>
+        <v>neispravni migavci ili maglenke.</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B103" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C103" t="str">
-        <v>Točkovi i gume</v>
+        <v>Rasveta</v>
       </c>
       <c r="D103" t="str">
-        <v>Ogrebotine na alu-felnama, ,</v>
+        <v>neispravni migavci ili maglenke.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B104" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C104" t="str">
-        <v>Točkovi i gume</v>
+        <v>Kamere i senzori</v>
       </c>
       <c r="D104" t="str">
-        <v xml:space="preserve">pogrešan smer rotacije gume, </v>
+        <v>Labavost parking senzora (upali unutra), ,</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B105" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C105" t="str">
-        <v>Točkovi i gume</v>
+        <v>Kamere i senzori</v>
       </c>
       <c r="D105" t="str">
-        <v>nedovoljan pritisak</v>
+        <v>prljava ili izgrebana sočiva kamera (rikverc/360)</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-EL-001</v>
       </c>
       <c r="B106" t="str">
-        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
       </c>
       <c r="C106" t="str">
-        <v>Točkovi i gume</v>
+        <v>Kamere i senzori</v>
       </c>
       <c r="D106" t="str">
-        <v xml:space="preserve"> nedostatak kapica na ventilima.</v>
+        <v>loša kalibracija radara.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B107" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C107" t="str">
-        <v>Rasveta</v>
+        <v>Prtljažni prostor</v>
       </c>
       <c r="D107" t="str">
-        <v xml:space="preserve">Kondenzacija (vlaga) unutar fara/stop svetla, , , </v>
+        <v>Labav pod gepeka, ,</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B108" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C108" t="str">
-        <v>Rasveta</v>
+        <v>Prtljažni prostor</v>
       </c>
       <c r="D108" t="str">
-        <v>nefunkcionalna LED traka</v>
+        <v>oštećenje bočnih tapacirunga</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B109" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C109" t="str">
-        <v>Rasveta</v>
+        <v>Prtljažni prostor</v>
       </c>
       <c r="D109" t="str">
-        <v>loš intenzitet svetla</v>
+        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B110" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C110" t="str">
-        <v>Rasveta</v>
+        <v>Prtljažni prostor</v>
       </c>
       <c r="D110" t="str">
-        <v>neispravni migavci ili maglenke.</v>
+        <v>neispravno svetlo gepeka.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B111" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C111" t="str">
-        <v>Rasveta</v>
+        <v>Funkcionalni test</v>
       </c>
       <c r="D111" t="str">
-        <v>neispravni migavci ili maglenke.</v>
+        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B112" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C112" t="str">
-        <v>Kamere i senzori</v>
+        <v>Funkcionalni test</v>
       </c>
       <c r="D112" t="str">
-        <v xml:space="preserve"> Labavost parking senzora (upali unutra), , </v>
+        <v>neispravna klima/grejanje</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B113" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C113" t="str">
-        <v>Kamere i senzori</v>
+        <v>Funkcionalni test</v>
       </c>
       <c r="D113" t="str">
-        <v>prljava ili izgrebana sočiva kamera (rikverc/360)</v>
+        <v>otkaz električne ručne kočnice</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B114" t="str">
-        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
       </c>
       <c r="C114" t="str">
-        <v>Kamere i senzori</v>
+        <v>Funkcionalni test</v>
       </c>
       <c r="D114" t="str">
-        <v>loša kalibracija radara.</v>
+        <v>otkaz električne ručne kočnice</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B115" t="str">
         <v>OSTALO</v>
@@ -4053,7 +4821,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B116" t="str">
         <v>OSTALO</v>
@@ -4062,12 +4830,12 @@
         <v>Ostalo</v>
       </c>
       <c r="D116" t="str">
-        <v xml:space="preserve"> tragovi voska za zaštitu</v>
+        <v>tragovi voska za zaštitu</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B117" t="str">
         <v>OSTALO</v>
@@ -4081,7 +4849,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>FINAL-001</v>
+        <v>NTV-FINAL-001</v>
       </c>
       <c r="B118" t="str">
         <v>OSTALO</v>
@@ -4093,50 +4861,3335 @@
         <v>nepravilna prateća dokumentacija u vozilu</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B119" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Loše poravnanje (zazor) sa krilima/farovima</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B120" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D120" t="str">
+        <v>labav spoj</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B121" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D121" t="str">
+        <v>ogrebotine</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B122" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D122" t="str">
+        <v>oštećenja plastike</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B123" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D123" t="str">
+        <v>neispravne žabice</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B124" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Nejednak zazor levo/desno</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B125" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D125" t="str">
+        <v>visinsko odstupanje u odnosu na krila</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B126" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D126" t="str">
+        <v>oštećenja boje (tačke, prašina u laku)</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B127" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D127" t="str">
+        <v>loše zatvaranje bravice.</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B128" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D128" t="str">
+        <v>buka</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B129" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Ogrebotine,,</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B130" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+      <c r="D130" t="str">
+        <v>ulubljenja (kontura)</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B131" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+      <c r="D131" t="str">
+        <v>loš spoj sa pragom i A-stubom.</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B132" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Ogrebotine,,</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B133" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+      <c r="D133" t="str">
+        <v>ulubljenja (kontura)</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B134" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+      <c r="D134" t="str">
+        <v>loš spoj sa pragom i A-stubom.</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B135" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Loš zazor/poravnanje, , , .</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B136" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D136" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B137" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D137" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B138" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D138" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B139" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Loš zazor/poravnanje, , , .</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B140" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D140" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B141" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D141" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B142" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D142" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B143" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Loš zazor/poravnanje, , , .</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B144" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D144" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B145" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D145" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B146" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D146" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B147" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D147" t="str">
+        <v>provera bezbednosne brave za decu (Child lock).</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B148" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Loš zazor/poravnanje</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B149" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D149" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B150" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D150" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B151" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D151" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B152" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D152" t="str">
+        <v>provera bezbednosne brave za decu (Child lock).</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B153" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Deformacije lima</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B154" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+      <c r="D154" t="str">
+        <v>prelazi boja na spojevima</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B155" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+      <c r="D155" t="str">
+        <v>loš spoj sa C-stubom i branikom</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B156" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Deformacije lima</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B157" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D157" t="str">
+        <v>prelazi boja na spojevima</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B158" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D158" t="str">
+        <v>loš spoj sa C-stubom i branikom</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B159" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D159" t="str">
+        <v>poklopac rezervoara/priključka za punjenje (labavost, zazor)</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B160" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Zadnji branik</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Loše poravnanje sa svetlima i krilima, i.</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B161" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Zadnji branik</v>
+      </c>
+      <c r="D161" t="str">
+        <v>ogrebotine pri dnu,</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B162" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Zadnji branik</v>
+      </c>
+      <c r="D162" t="str">
+        <v>labavi nosač</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B163" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Teško zatvaranje,</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B164" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D164" t="str">
+        <v>neujednačen zazor sa svetlosnim grupama</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B165" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D165" t="str">
+        <v>visinska odstupanja,</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B166" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D166" t="str">
+        <v>loše zaptivanje gume.</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B167" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Krov</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Talasi na limu</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B168" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Krov</v>
+      </c>
+      <c r="D168" t="str">
+        <v>oštećenja boje od transporta</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B169" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Krov</v>
+      </c>
+      <c r="D169" t="str">
+        <v>loš spoj krovnih lajsni ili panoramskog stakla</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B170" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Pukotine (zvezdice)</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B171" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D171" t="str">
+        <v>ogrebotine od brisača</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B172" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D172" t="str">
+        <v>loša aplikacija lepka (curenje vode)</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B173" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D173" t="str">
+        <v>fabrički mehurići u staklu.</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B174" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Bočna stakla</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Ogrebotine od podizanja/spuštanja,</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B175" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Bočna stakla</v>
+      </c>
+      <c r="D175" t="str">
+        <v>zazor pri zatvaranju (prolaz vazduha),</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>MRAP-KAROS-001</v>
+      </c>
+      <c r="B176" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Bočna stakla</v>
+      </c>
+      <c r="D176" t="str">
+        <v>oštećenja toniranog filma.</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>MRAP-MOTOR-001</v>
+      </c>
+      <c r="B177" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona),</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>MRAP-MOTOR-001</v>
+      </c>
+      <c r="B178" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D178" t="str">
+        <v>labave obujmice creva</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>MRAP-MOTOR-001</v>
+      </c>
+      <c r="B179" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D179" t="str">
+        <v>nepravilno rutirani kablovi</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>MRAP-MOTOR-001</v>
+      </c>
+      <c r="B180" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D180" t="str">
+        <v>nedostatak plastičnih poklopaca.</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B181" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Curenje tečnosti na spojevima (menjač, karter), , ,</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B182" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D182" t="str">
+        <v>labave zaštitne plastike (šuspleh)</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B183" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D183" t="str">
+        <v>korozija na spojevima</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B184" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D184" t="str">
+        <v>loše zategnuti elementi oslanjanja.</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B185" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Ogrebotine na alu-felnama, ,</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B186" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D186" t="str">
+        <v>pogrešan smer rotacije gume,</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B187" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D187" t="str">
+        <v>nedovoljan pritisak</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>MRAP-TRANS-001</v>
+      </c>
+      <c r="B188" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D188" t="str">
+        <v>nedostatak kapica na ventilima.</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Loš zazor na spojevima plastika,, , .</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B190" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D190" t="str">
+        <v>cvrčanje/škripa pri pritisku</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B191" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D191" t="str">
+        <v>ogrebotine na mekim površinama</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B192" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D192" t="str">
+        <v>loše uklopljen vazdušni jastuk suvozača</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B193" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Labavost naslona za ruku, , ,.</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B194" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D194" t="str">
+        <v>loš hod poklopaca/pregrada</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B195" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D195" t="str">
+        <v>ogrebotine na sjajnim (Piano black) površinama</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B196" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D196" t="str">
+        <v>labava ručica menjača</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B197" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Oštećenje šavova,, .</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B198" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D198" t="str">
+        <v>naborana koža/tkanina</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B199" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D199" t="str">
+        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B200" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D200" t="str">
+        <v>klimanje sedišta u šinama</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B201" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Oštećenje šavova,, .</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B202" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D202" t="str">
+        <v>naborana koža/tkanina</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B203" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D203" t="str">
+        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B204" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D204" t="str">
+        <v>klimanje sedišta u šinama</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B205" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Loše fiksiran donji deo klupe,</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B206" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+      <c r="D206" t="str">
+        <v>problem sa preklapanjem naslona,</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B207" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+      <c r="D207" t="str">
+        <v>oštećenja ISOFIX priključaka.</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B208" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Oštećenja tapacirunga krova (nebo),</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B209" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D209" t="str">
+        <v>ogrebotine na oblogama stubova (A, B, C),</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B210" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D210" t="str">
+        <v>labavi rukohvati na krovu,</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>MRAP-INT-001</v>
+      </c>
+      <c r="B211" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D211" t="str">
+        <v>loše postavljeni tepisi/patosnice.</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B212" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Greška na instrument tabli, , ,</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B213" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D213" t="str">
+        <v>nefunkcionalan USB/12V priključak</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B214" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D214" t="str">
+        <v>otkaz podizača prozora</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B215" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D215" t="str">
+        <v>problem sa audio sistemom.</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B216" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Kondenzacija (vlaga) unutar fara/stop svetla, , ,</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B217" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D217" t="str">
+        <v>nefunkcionalna LED traka</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B218" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D218" t="str">
+        <v>loš intenzitet svetla</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B219" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D219" t="str">
+        <v>neispravni migavci ili maglenke.</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B220" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D220" t="str">
+        <v>neispravni migavci ili maglenke.</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B221" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Labavost parking senzora (upali unutra), ,</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B222" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+      <c r="D222" t="str">
+        <v>prljava ili izgrebana sočiva kamera (rikverc/360)</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>MRAP-EL-001</v>
+      </c>
+      <c r="B223" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+      <c r="D223" t="str">
+        <v>loša kalibracija radara.</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B224" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Labav pod gepeka, ,</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B225" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D225" t="str">
+        <v>oštećenje bočnih tapacirunga</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B226" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D226" t="str">
+        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B227" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D227" t="str">
+        <v>neispravno svetlo gepeka.</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B228" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B229" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D229" t="str">
+        <v>neispravna klima/grejanje</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B230" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D230" t="str">
+        <v>otkaz električne ručne kočnice</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B231" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D231" t="str">
+        <v>otkaz električne ručne kočnice</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B232" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Prljavština na vozilu,, , .</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B233" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D233" t="str">
+        <v>tragovi voska za zaštitu</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B234" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D234" t="str">
+        <v>nedostajuće zaštitne folije</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>MRAP-FINAL-001</v>
+      </c>
+      <c r="B235" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D235" t="str">
+        <v>nepravilna prateća dokumentacija u vozilu</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B236" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Loše poravnanje (zazor) sa krilima/farovima</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B237" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D237" t="str">
+        <v>labav spoj</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B238" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D238" t="str">
+        <v>ogrebotine</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B239" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D239" t="str">
+        <v>oštećenja plastike</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B240" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Prednji branik</v>
+      </c>
+      <c r="D240" t="str">
+        <v>neispravne žabice</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B241" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Nejednak zazor levo/desno</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B242" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D242" t="str">
+        <v>visinsko odstupanje u odnosu na krila</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B243" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D243" t="str">
+        <v>oštećenja boje (tačke, prašina u laku)</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B244" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D244" t="str">
+        <v>loše zatvaranje bravice.</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B245" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Hauba</v>
+      </c>
+      <c r="D245" t="str">
+        <v>buka</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B246" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Ogrebotine,,</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B247" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+      <c r="D247" t="str">
+        <v>ulubljenja (kontura)</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B248" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Levo prednje krilo</v>
+      </c>
+      <c r="D248" t="str">
+        <v>loš spoj sa pragom i A-stubom.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B249" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Ogrebotine,,</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B250" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+      <c r="D250" t="str">
+        <v>ulubljenja (kontura)</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B251" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Desno prednje krilo</v>
+      </c>
+      <c r="D251" t="str">
+        <v>loš spoj sa pragom i A-stubom.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B252" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Loš zazor/poravnanje, , , .</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B253" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D253" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B254" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D254" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B255" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Leva prednja vrata</v>
+      </c>
+      <c r="D255" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B256" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Loš zazor/poravnanje, , , .</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B257" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D257" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B258" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D258" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B259" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Desna prednja vrata</v>
+      </c>
+      <c r="D259" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B260" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Loš zazor/poravnanje, , , .</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B261" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D261" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B262" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D262" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B263" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D263" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B264" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Leva zadnja vrata</v>
+      </c>
+      <c r="D264" t="str">
+        <v>provera bezbednosne brave za decu (Child lock).</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B265" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Loš zazor/poravnanje</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B266" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D266" t="str">
+        <v>zvuk škripanja pri otvaranju</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B267" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D267" t="str">
+        <v>ogrebotine oko kvake</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B268" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D268" t="str">
+        <v>loše nalepljena zaptivna guma (kedera)</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B269" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Desna zadnja vrata</v>
+      </c>
+      <c r="D269" t="str">
+        <v>provera bezbednosne brave za decu (Child lock).</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B270" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Deformacije lima</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B271" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+      <c r="D271" t="str">
+        <v>prelazi boja na spojevima</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B272" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Zadnje levo krilo</v>
+      </c>
+      <c r="D272" t="str">
+        <v>loš spoj sa C-stubom i branikom</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B273" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Deformacije lima</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B274" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D274" t="str">
+        <v>prelazi boja na spojevima</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B275" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D275" t="str">
+        <v>loš spoj sa C-stubom i branikom</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B276" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Zadnje desno krilo</v>
+      </c>
+      <c r="D276" t="str">
+        <v>poklopac rezervoara/priključka za punjenje (labavost, zazor)</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B277" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Zadnji branik</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Loše poravnanje sa svetlima i krilima, i.</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B278" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Zadnji branik</v>
+      </c>
+      <c r="D278" t="str">
+        <v>ogrebotine pri dnu,</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B279" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Zadnji branik</v>
+      </c>
+      <c r="D279" t="str">
+        <v>labavi nosač</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B280" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Teško zatvaranje,</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B281" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D281" t="str">
+        <v>neujednačen zazor sa svetlosnim grupama</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B282" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D282" t="str">
+        <v>visinska odstupanja,</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B283" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Poklopac gepeka</v>
+      </c>
+      <c r="D283" t="str">
+        <v>loše zaptivanje gume.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B284" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Krov</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Talasi na limu</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B285" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Krov</v>
+      </c>
+      <c r="D285" t="str">
+        <v>oštećenja boje od transporta</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B286" t="str">
+        <v>EKSTERIJER (Karoserija i Limarija)</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Krov</v>
+      </c>
+      <c r="D286" t="str">
+        <v>loš spoj krovnih lajsni ili panoramskog stakla</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B287" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Pukotine (zvezdice)</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B288" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D288" t="str">
+        <v>ogrebotine od brisača</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B289" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D289" t="str">
+        <v>loša aplikacija lepka (curenje vode)</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B290" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Vetrobran</v>
+      </c>
+      <c r="D290" t="str">
+        <v>fabrički mehurići u staklu.</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B291" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Bočna stakla</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Ogrebotine od podizanja/spuštanja,</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B292" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Bočna stakla</v>
+      </c>
+      <c r="D292" t="str">
+        <v>zazor pri zatvaranju (prolaz vazduha),</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>MRAP1-KAROS-001</v>
+      </c>
+      <c r="B293" t="str">
+        <v>STAKLENE POVRŠINE</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Bočna stakla</v>
+      </c>
+      <c r="D293" t="str">
+        <v>oštećenja toniranog filma.</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>MRAP1-MOTOR-001</v>
+      </c>
+      <c r="B294" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D294" t="str">
+        <v>Nizak nivo tečnosti (ulje, rashladna, kočiona),</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>MRAP1-MOTOR-001</v>
+      </c>
+      <c r="B295" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D295" t="str">
+        <v>labave obujmice creva</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>MRAP1-MOTOR-001</v>
+      </c>
+      <c r="B296" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D296" t="str">
+        <v>nepravilno rutirani kablovi</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>MRAP1-MOTOR-001</v>
+      </c>
+      <c r="B297" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Motorni prostor</v>
+      </c>
+      <c r="D297" t="str">
+        <v>nedostatak plastičnih poklopaca.</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B298" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D298" t="str">
+        <v>Curenje tečnosti na spojevima (menjač, karter), , ,</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B299" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D299" t="str">
+        <v>labave zaštitne plastike (šuspleh)</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B300" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D300" t="str">
+        <v>korozija na spojevima</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B301" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Podvozje</v>
+      </c>
+      <c r="D301" t="str">
+        <v>loše zategnuti elementi oslanjanja.</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B302" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Ogrebotine na alu-felnama, ,</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B303" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C303" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D303" t="str">
+        <v>pogrešan smer rotacije gume,</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B304" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C304" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D304" t="str">
+        <v>nedovoljan pritisak</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>MRAP1-TRANS-001</v>
+      </c>
+      <c r="B305" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C305" t="str">
+        <v>Točkovi i gume</v>
+      </c>
+      <c r="D305" t="str">
+        <v>nedostatak kapica na ventilima.</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B306" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C306" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Loš zazor na spojevima plastika,, , .</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B307" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C307" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D307" t="str">
+        <v>cvrčanje/škripa pri pritisku</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B308" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C308" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D308" t="str">
+        <v>ogrebotine na mekim površinama</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B309" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C309" t="str">
+        <v>Instrument tabla</v>
+      </c>
+      <c r="D309" t="str">
+        <v>loše uklopljen vazdušni jastuk suvozača</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B310" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C310" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Labavost naslona za ruku, , ,.</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B311" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C311" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D311" t="str">
+        <v>loš hod poklopaca/pregrada</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B312" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C312" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D312" t="str">
+        <v>ogrebotine na sjajnim (Piano black) površinama</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B313" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C313" t="str">
+        <v>Centralna konzola</v>
+      </c>
+      <c r="D313" t="str">
+        <v>labava ručica menjača</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B314" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C314" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Oštećenje šavova,, .</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B315" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D315" t="str">
+        <v>naborana koža/tkanina</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B316" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D316" t="str">
+        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B317" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C317" t="str">
+        <v>Sedište vozača</v>
+      </c>
+      <c r="D317" t="str">
+        <v>klimanje sedišta u šinama</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B318" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C318" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Oštećenje šavova,, .</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B319" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C319" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D319" t="str">
+        <v>naborana koža/tkanina</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B320" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D320" t="str">
+        <v>neispravan mehanizam pomeranja (ručni/elektro),</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B321" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Sedište suvozača</v>
+      </c>
+      <c r="D321" t="str">
+        <v>klimanje sedišta u šinama</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B322" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Loše fiksiran donji deo klupe,</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B323" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C323" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+      <c r="D323" t="str">
+        <v>problem sa preklapanjem naslona,</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B324" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C324" t="str">
+        <v>Zadnja sedišta</v>
+      </c>
+      <c r="D324" t="str">
+        <v>oštećenja ISOFIX priključaka.</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B325" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C325" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Oštećenja tapacirunga krova (nebo),</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B326" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D326" t="str">
+        <v>ogrebotine na oblogama stubova (A, B, C),</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B327" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C327" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D327" t="str">
+        <v>labavi rukohvati na krovu,</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>MRAP1-INT-001</v>
+      </c>
+      <c r="B328" t="str">
+        <v>ENTERIJER (Kabina)</v>
+      </c>
+      <c r="C328" t="str">
+        <v>Enterijer</v>
+      </c>
+      <c r="D328" t="str">
+        <v>loše postavljeni tepisi/patosnice.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B329" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C329" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Greška na instrument tabli, , ,</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B330" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C330" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D330" t="str">
+        <v>nefunkcionalan USB/12V priključak</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B331" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C331" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D331" t="str">
+        <v>otkaz podizača prozora</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B332" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C332" t="str">
+        <v>Elektrika</v>
+      </c>
+      <c r="D332" t="str">
+        <v>problem sa audio sistemom.</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B333" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C333" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Kondenzacija (vlaga) unutar fara/stop svetla, , ,</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B334" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C334" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D334" t="str">
+        <v>nefunkcionalna LED traka</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B335" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C335" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D335" t="str">
+        <v>loš intenzitet svetla</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B336" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C336" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D336" t="str">
+        <v>neispravni migavci ili maglenke.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B337" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C337" t="str">
+        <v>Rasveta</v>
+      </c>
+      <c r="D337" t="str">
+        <v>neispravni migavci ili maglenke.</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B338" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C338" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Labavost parking senzora (upali unutra), ,</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B339" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C339" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+      <c r="D339" t="str">
+        <v>prljava ili izgrebana sočiva kamera (rikverc/360)</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>MRAP1-EL-001</v>
+      </c>
+      <c r="B340" t="str">
+        <v>OSVETLJENJE, SIGNALIZACIJA I SENZORI</v>
+      </c>
+      <c r="C340" t="str">
+        <v>Kamere i senzori</v>
+      </c>
+      <c r="D340" t="str">
+        <v>loša kalibracija radara.</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B341" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C341" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Labav pod gepeka, ,</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B342" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C342" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D342" t="str">
+        <v>oštećenje bočnih tapacirunga</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B343" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C343" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D343" t="str">
+        <v>nedostatak prateće opreme (rezervni točak/kit, dizalica),</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B344" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Prtljažni prostor</v>
+      </c>
+      <c r="D344" t="str">
+        <v>neispravno svetlo gepeka.</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B345" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Loš odziv multimedije (ekrana na dodir), , .</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B346" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D346" t="str">
+        <v>neispravna klima/grejanje</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B347" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D347" t="str">
+        <v>otkaz električne ručne kočnice</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B348" t="str">
+        <v>FUNKCIONALNE ZONE I PODVOZJE</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Funkcionalni test</v>
+      </c>
+      <c r="D348" t="str">
+        <v>otkaz električne ručne kočnice</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B349" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Prljavština na vozilu,, , .</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B350" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D350" t="str">
+        <v>tragovi voska za zaštitu</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B351" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C351" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D351" t="str">
+        <v>nedostajuće zaštitne folije</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>MRAP1-FINAL-001</v>
+      </c>
+      <c r="B352" t="str">
+        <v>OSTALO</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Ostalo</v>
+      </c>
+      <c r="D352" t="str">
+        <v>nepravilna prateća dokumentacija u vozilu</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D352"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id dela*</v>
       </c>
       <c r="B1" t="str">
+        <v>pogon kod</v>
+      </c>
+      <c r="C1" t="str">
+        <v>radni nalog</v>
+      </c>
+      <c r="D1" t="str">
         <v>naziv dela*</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>karakteristika kontrole*</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>linija id*</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>masina id*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>kom za kontrolu n*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>slika/crtez</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>aktivan</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>napomena</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>tip kontrole</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>vozilo katalog id</v>
+      </c>
+      <c r="N1" t="str">
+        <v>greska katalog id</v>
       </c>
     </row>
     <row r="2">
@@ -4144,31 +8197,43 @@
         <v>5501-A</v>
       </c>
       <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v>Nosac</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>Vizuelna kontrola vara i zazora</v>
       </c>
-      <c r="D2">
+      <c r="F2" t="str">
         <v>12</v>
       </c>
-      <c r="E2">
+      <c r="G2" t="str">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="H2" t="str">
         <v>30</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Nosac_SOP.jpg</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>DA</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>Karoserija linija</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>deo</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -4176,31 +8241,43 @@
         <v>5502-A</v>
       </c>
       <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
         <v>Osovina</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E3" t="str">
         <v>Vizuelna kontrola povrsine i montaze</v>
       </c>
-      <c r="D3">
+      <c r="F3" t="str">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="G3" t="str">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="H3" t="str">
         <v>20</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Osovina_SOP.jpg</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>DA</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>Preseraj linija</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>deo</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -4208,31 +8285,43 @@
         <v>5503-A</v>
       </c>
       <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
         <v>Poklopac</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E4" t="str">
         <v>Kontrola zazora i brtvljenja</v>
       </c>
-      <c r="D4">
+      <c r="F4" t="str">
         <v>30</v>
       </c>
-      <c r="E4">
+      <c r="G4" t="str">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="H4" t="str">
         <v>25</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Poklopac_SOP.jpg</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>DA</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>Montaza finalna</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>deo</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -4240,25 +8329,43 @@
         <v>5504-B</v>
       </c>
       <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <v>Nosac motor</v>
       </c>
-      <c r="C5" t="str">
+      <c r="E5" t="str">
         <v>Vizuelna i funkcionalna kontrola</v>
       </c>
-      <c r="D5">
+      <c r="F5" t="str">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="G5" t="str">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="H5" t="str">
         <v>30</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
         <v>DA</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>deo</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -4266,517 +8373,1103 @@
         <v>5505-B</v>
       </c>
       <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
         <v>Konzola</v>
       </c>
-      <c r="C6" t="str">
+      <c r="E6" t="str">
         <v>Kontrola vara i dimenzija</v>
       </c>
-      <c r="D6">
+      <c r="F6" t="str">
         <v>12</v>
       </c>
-      <c r="E6">
+      <c r="G6" t="str">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="H6" t="str">
         <v>20</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
         <v>DA</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>deo</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AUTO-001</v>
+        <v>MRAP-001</v>
       </c>
       <c r="B7" t="str">
-        <v>Automobil-komplet</v>
+        <v/>
       </c>
       <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>MRAP komplet</v>
+      </c>
+      <c r="E7" t="str">
         <v>Finalna vizuelna kontrola celog vozila</v>
       </c>
-      <c r="D7">
+      <c r="F7" t="str">
         <v>48</v>
       </c>
-      <c r="E7">
+      <c r="G7" t="str">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="H7" t="str">
         <v>5</v>
       </c>
-      <c r="G7" t="str">
-        <v>Auto_final_SOP.jpg</v>
-      </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
+        <v>MRAP_SOP.jpg</v>
+      </c>
+      <c r="J7" t="str">
         <v>DA</v>
       </c>
-      <c r="I7" t="str">
-        <v>Koristiti za finalnu kontrolu</v>
-      </c>
-      <c r="J7" t="str">
+      <c r="K7" t="str">
+        <v>MRAP — oklopno vozilo</v>
+      </c>
+      <c r="L7" t="str">
         <v>vozilo</v>
       </c>
-      <c r="K7" t="str">
-        <v>FINAL-001</v>
+      <c r="M7" t="str">
+        <v>MRAP</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>MRAP1-001</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>MRAP1 komplet</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="F8" t="str">
+        <v>48</v>
+      </c>
+      <c r="G8" t="str">
+        <v>1</v>
+      </c>
+      <c r="H8" t="str">
+        <v>5</v>
+      </c>
+      <c r="I8" t="str">
+        <v>MRAP1_SOP.jpg</v>
+      </c>
+      <c r="J8" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K8" t="str">
+        <v>MRAP1 — oklopno vozilo 6x6</v>
+      </c>
+      <c r="L8" t="str">
+        <v>vozilo</v>
+      </c>
+      <c r="M8" t="str">
+        <v>MRAP1</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>A</v>
+      </c>
+      <c r="C9" t="str">
+        <v>RN-2026-NM001-A</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Vizuelna kontrola ulazna</v>
+      </c>
+      <c r="F9" t="str">
+        <v>43</v>
+      </c>
+      <c r="G9" t="str">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v>5</v>
+      </c>
+      <c r="I9" t="str">
+        <v>NM-01.png</v>
+      </c>
+      <c r="J9" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Atributivne — Ulazna</v>
+      </c>
+      <c r="L9" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>C</v>
+      </c>
+      <c r="C10" t="str">
+        <v>RN-2026-NM001-C</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Vizuelna kontrola zavarivanje</v>
+      </c>
+      <c r="F10" t="str">
+        <v>12</v>
+      </c>
+      <c r="G10" t="str">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
+        <v>5</v>
+      </c>
+      <c r="I10" t="str">
+        <v>NM-01.png</v>
+      </c>
+      <c r="J10" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Atributivne — Karoserija</v>
+      </c>
+      <c r="L10" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>F</v>
+      </c>
+      <c r="C11" t="str">
+        <v>RN-2026-NM001-F</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Završna kontrola</v>
+      </c>
+      <c r="F11" t="str">
+        <v>48</v>
+      </c>
+      <c r="G11" t="str">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <v>4</v>
+      </c>
+      <c r="I11" t="str">
+        <v>NM-01.png</v>
+      </c>
+      <c r="J11" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Atributivne — Finalna</v>
+      </c>
+      <c r="L11" t="str">
+        <v>deo</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>NTV-001</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>NTV komplet</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Finalna vizuelna kontrola celog vozila</v>
+      </c>
+      <c r="F12" t="str">
+        <v>48</v>
+      </c>
+      <c r="G12" t="str">
+        <v>1</v>
+      </c>
+      <c r="H12" t="str">
+        <v>5</v>
+      </c>
+      <c r="I12" t="str">
+        <v>NTV_SOP.jpg</v>
+      </c>
+      <c r="J12" t="str">
+        <v>DA</v>
+      </c>
+      <c r="K12" t="str">
+        <v>NTV — novo terensko vozilo</v>
+      </c>
+      <c r="L12" t="str">
+        <v>vozilo</v>
+      </c>
+      <c r="M12" t="str">
+        <v>NTV</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>ime i prezime*</v>
+        <v>id dela</v>
       </c>
       <c r="C1" t="str">
-        <v>uloga*</v>
+        <v>naziv</v>
       </c>
       <c r="D1" t="str">
-        <v>email*</v>
+        <v>rty cilj %</v>
       </c>
       <c r="E1" t="str">
-        <v>supabase user_id</v>
+        <v>dpmo cilj</v>
       </c>
       <c r="F1" t="str">
-        <v>aktivan</v>
+        <v>p cilj %</v>
       </c>
       <c r="G1" t="str">
-        <v>napomena</v>
+        <v>vazi od</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rty ostvareno</v>
+      </c>
+      <c r="I1" t="str">
+        <v>dpmo ostvareno</v>
+      </c>
+      <c r="J1" t="str">
+        <v>p ostvareno</v>
+      </c>
+      <c r="K1" t="str">
+        <v>status rty</v>
+      </c>
+      <c r="L1" t="str">
+        <v>status dpmo</v>
+      </c>
+      <c r="M1" t="str">
+        <v>trend</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>5501-A</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Nosac</v>
+      </c>
+      <c r="D2" t="str">
+        <v>95</v>
+      </c>
+      <c r="E2" t="str">
+        <v>50000</v>
+      </c>
+      <c r="F2" t="str">
+        <v>5</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2024-01-01</v>
+      </c>
+      <c r="H2" t="str">
+        <v>92.3</v>
+      </c>
+      <c r="I2" t="str">
+        <v>77000</v>
+      </c>
+      <c r="J2" t="str">
+        <v>7.7</v>
+      </c>
+      <c r="K2" t="str">
+        <v>ISPOD</v>
+      </c>
+      <c r="L2" t="str">
+        <v>ISPOD</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Pogorsanje</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>PETROVIC DRAGOMIR</v>
+        <v>5502-A</v>
       </c>
       <c r="C3" t="str">
-        <v>kontrolor</v>
+        <v>Osovina</v>
       </c>
       <c r="D3" t="str">
-        <v>petrovic@fabrika.com</v>
+        <v>97</v>
       </c>
       <c r="E3" t="str">
-        <v>(auto iz Supabase Auth)</v>
+        <v>30000</v>
       </c>
       <c r="F3" t="str">
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="str">
-        <v>KIKA KON</v>
-      </c>
-      <c r="C5" t="str">
-        <v>kontrolor</v>
-      </c>
-      <c r="D5" t="str">
-        <v>kika@fabrika.com</v>
-      </c>
-      <c r="E5" t="str">
-        <v>(auto iz Supabase Auth)</v>
-      </c>
-      <c r="F5" t="str">
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" t="str">
-        <v>MIKA KON</v>
-      </c>
-      <c r="C7" t="str">
-        <v>kontrolor</v>
-      </c>
-      <c r="D7" t="str">
-        <v>mika@fabrika.com</v>
-      </c>
-      <c r="E7" t="str">
-        <v>(auto iz Supabase Auth)</v>
-      </c>
-      <c r="F7" t="str">
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9" t="str">
-        <v>PERA OPERATER</v>
-      </c>
-      <c r="C9" t="str">
-        <v>operator</v>
-      </c>
-      <c r="D9" t="str">
-        <v>pera@fabrika.com</v>
-      </c>
-      <c r="E9" t="str">
-        <v>(auto iz Supabase Auth)</v>
-      </c>
-      <c r="F9" t="str">
-        <v>DA</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
+      <c r="G3" t="str">
+        <v>2024-01-01</v>
+      </c>
+      <c r="H3" t="str">
+        <v>96.7</v>
+      </c>
+      <c r="I3" t="str">
+        <v>33000</v>
+      </c>
+      <c r="J3" t="str">
+        <v>3.3</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Blizu</v>
+      </c>
+      <c r="L3" t="str">
+        <v>ISPOD</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Stabilan</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>5503-A</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Poklopac</v>
+      </c>
+      <c r="D4" t="str">
+        <v>95</v>
+      </c>
+      <c r="E4" t="str">
+        <v>50000</v>
+      </c>
+      <c r="F4" t="str">
         <v>5</v>
       </c>
-      <c r="B11" t="str">
-        <v>ADMIN</v>
-      </c>
-      <c r="C11" t="str">
-        <v>admin</v>
-      </c>
-      <c r="D11" t="str">
-        <v>admin@fabrika.com</v>
-      </c>
-      <c r="E11" t="str">
-        <v>(auto iz Supabase Auth)</v>
-      </c>
-      <c r="F11" t="str">
-        <v>DA</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Sistem administrator</v>
+      <c r="G4" t="str">
+        <v>2024-01-01</v>
+      </c>
+      <c r="H4" t="str">
+        <v>98.1</v>
+      </c>
+      <c r="I4" t="str">
+        <v>19000</v>
+      </c>
+      <c r="J4" t="str">
+        <v>1.9</v>
+      </c>
+      <c r="K4" t="str">
+        <v>OK</v>
+      </c>
+      <c r="L4" t="str">
+        <v>OK</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Poboljsanje</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>radni nal</v>
+        <v>ime i prezime*</v>
       </c>
       <c r="C1" t="str">
-        <v>id dela*</v>
+        <v>uloga*</v>
       </c>
       <c r="D1" t="str">
-        <v>naziv dela</v>
+        <v>email*</v>
       </c>
       <c r="E1" t="str">
-        <v>količina</v>
+        <v>supabase user_id</v>
       </c>
       <c r="F1" t="str">
-        <v>kupac</v>
+        <v>aktivan</v>
       </c>
       <c r="G1" t="str">
-        <v>datum unosa</v>
-      </c>
-      <c r="H1" t="str">
-        <v>rok isporuke</v>
-      </c>
-      <c r="I1" t="str">
-        <v>status</v>
-      </c>
-      <c r="J1" t="str">
-        <v>operater</v>
-      </c>
-      <c r="K1" t="str">
         <v>napomena</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>RN-2024-001</v>
+        <v>PETROVIC DRAGOMIR</v>
       </c>
       <c r="C2" t="str">
-        <v>5501-A</v>
+        <v>kontrolor</v>
       </c>
       <c r="D2" t="str">
-        <v>Nosac</v>
-      </c>
-      <c r="E2">
-        <v>500</v>
+        <v>petrovic@fabrika.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v>(auto iz Supabase Auth)</v>
       </c>
       <c r="F2" t="str">
-        <v>Kupac A</v>
-      </c>
-      <c r="G2">
-        <v>45306.041666666664</v>
-      </c>
-      <c r="H2">
-        <v>45337.041666666664</v>
-      </c>
-      <c r="I2" t="str">
-        <v>aktivan</v>
-      </c>
-      <c r="J2" t="str">
+        <v>DA</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>KIKA KON</v>
+      </c>
+      <c r="C3" t="str">
+        <v>kontrolor</v>
+      </c>
+      <c r="D3" t="str">
+        <v>kika@fabrika.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v>(auto iz Supabase Auth)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>DA</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>MIKA KON</v>
+      </c>
+      <c r="C4" t="str">
+        <v>kontrolor</v>
+      </c>
+      <c r="D4" t="str">
+        <v>mika@fabrika.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v>(auto iz Supabase Auth)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>DA</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
         <v>PERA OPERATER</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>RN-2024-002</v>
-      </c>
-      <c r="C3" t="str">
-        <v>5502-A</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Osovina</v>
-      </c>
-      <c r="E3">
-        <v>300</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Kupac B</v>
-      </c>
-      <c r="G3">
-        <v>45307.041666666664</v>
-      </c>
-      <c r="H3">
-        <v>45342.041666666664</v>
-      </c>
-      <c r="I3" t="str">
-        <v>aktivan</v>
-      </c>
-      <c r="J3" t="str">
-        <v>PERA OPERATER</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Hitna isporuka</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>RN-2024-003</v>
-      </c>
-      <c r="C4" t="str">
-        <v>5503-A</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Poklopac</v>
-      </c>
-      <c r="E4">
-        <v>200</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Kupac A</v>
-      </c>
-      <c r="G4">
-        <v>45311.041666666664</v>
-      </c>
-      <c r="H4">
-        <v>45352.041666666664</v>
-      </c>
-      <c r="I4" t="str">
-        <v>aktivan</v>
-      </c>
-      <c r="J4" t="str">
-        <v>PERA OPERATER</v>
+      <c r="C5" t="str">
+        <v>operator</v>
+      </c>
+      <c r="D5" t="str">
+        <v>pera@fabrika.com</v>
+      </c>
+      <c r="E5" t="str">
+        <v>(auto iz Supabase Auth)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DA</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="C6" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D6" t="str">
+        <v>admin@fabrika.com</v>
+      </c>
+      <c r="E6" t="str">
+        <v>(auto iz Supabase Auth)</v>
+      </c>
+      <c r="F6" t="str">
+        <v>DA</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Sistem administrator</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>kategorija</v>
+        <v>radni nal</v>
       </c>
       <c r="C1" t="str">
-        <v>stavka</v>
+        <v>id dela*</v>
       </c>
       <c r="D1" t="str">
-        <v>redosled</v>
+        <v>naziv dela</v>
       </c>
       <c r="E1" t="str">
-        <v>aktivna</v>
+        <v>količina</v>
+      </c>
+      <c r="F1" t="str">
+        <v>kupac</v>
+      </c>
+      <c r="G1" t="str">
+        <v>datum unosa</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rok isporuke</v>
+      </c>
+      <c r="I1" t="str">
+        <v>status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>operater</v>
+      </c>
+      <c r="K1" t="str">
+        <v>napomena</v>
+      </c>
+      <c r="L1" t="str">
+        <v>pogon_kod</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>BEZBEDNOST</v>
+        <v>RN-2024-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Proverena lična zaštitna oprema (rukavice</v>
+        <v>5501-A</v>
       </c>
       <c r="D2" t="str">
-        <v xml:space="preserve"> naočari</v>
+        <v>Nosac</v>
       </c>
       <c r="E2" t="str">
-        <v xml:space="preserve"> obuća)</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>500</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Kupac A</v>
       </c>
       <c r="G2" t="str">
-        <v>DA</v>
+        <v>2024-01-15</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2024-02-15</v>
+      </c>
+      <c r="I2" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J2" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>BEZBEDNOST</v>
+        <v>RN-2024-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Radno mesto je čisto i bez prepreka</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>5502-A</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Osovina</v>
       </c>
       <c r="E3" t="str">
-        <v>DA</v>
+        <v>300</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Kupac B</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2024-01-16</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2024-02-20</v>
+      </c>
+      <c r="I3" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J3" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Hitna isporuka</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>OPREMA</v>
+        <v>RN-2024-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Mašina/alat je ispravan i spreman za rad</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
+        <v>5503-A</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Poklopac</v>
       </c>
       <c r="E4" t="str">
-        <v>DA</v>
+        <v>200</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Kupac A</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2024-01-20</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="I4" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J4" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>10</v>
       </c>
       <c r="B5" t="str">
-        <v>OPREMA</v>
+        <v>RN-2026-NM001-A</v>
       </c>
       <c r="C5" t="str">
-        <v>Merila su dostupna i kalibrisana</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
+        <v>NM-001</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Nosač motora</v>
       </c>
       <c r="E5" t="str">
-        <v>DA</v>
+        <v>50</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I5" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J5" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K5" t="str">
+        <v>A</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>11</v>
       </c>
       <c r="B6" t="str">
-        <v>DOKUMENTACIJA</v>
+        <v>RN-2026-NM001-B</v>
       </c>
       <c r="C6" t="str">
-        <v>Radni nalog i crtež dela su dostupni</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
+        <v>NM-001</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Nosač motora</v>
       </c>
       <c r="E6" t="str">
-        <v>DA</v>
+        <v>50</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I6" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J6" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K6" t="str">
+        <v>B</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>12</v>
       </c>
       <c r="B7" t="str">
-        <v>DOKUMENTACIJA</v>
+        <v>RN-2026-NM001-C</v>
       </c>
       <c r="C7" t="str">
-        <v>SOP / uputstvo za kontrolu je pročitano</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
+        <v>NM-001</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Nosač motora</v>
       </c>
       <c r="E7" t="str">
-        <v>DA</v>
+        <v>50</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I7" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J7" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K7" t="str">
+        <v>C</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>13</v>
       </c>
       <c r="B8" t="str">
-        <v>MATERIJAL</v>
+        <v>RN-2026-NM001-D</v>
       </c>
       <c r="C8" t="str">
-        <v>Materijal i delovi odgovaraju radnom nalogu</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
+        <v>NM-001</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Nosač motora</v>
       </c>
       <c r="E8" t="str">
-        <v>DA</v>
+        <v>50</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I8" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J8" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K8" t="str">
+        <v>D</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>14</v>
       </c>
       <c r="B9" t="str">
-        <v>KVALITET</v>
+        <v>RN-2026-NM001-E</v>
       </c>
       <c r="C9" t="str">
-        <v>Prethodna smena ostavila napomenu — provereno</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
+        <v>NM-001</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Nosač motora</v>
       </c>
       <c r="E9" t="str">
-        <v>DA</v>
+        <v>50</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I9" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J9" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K9" t="str">
+        <v>E</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>15</v>
+      </c>
+      <c r="B10" t="str">
+        <v>RN-2026-NM001-F</v>
+      </c>
+      <c r="C10" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E10" t="str">
+        <v>50</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H10" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I10" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J10" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K10" t="str">
+        <v>F</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>16</v>
+      </c>
+      <c r="B11" t="str">
+        <v>RN-2026-NM001-G</v>
+      </c>
+      <c r="C11" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E11" t="str">
+        <v>50</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I11" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J11" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K11" t="str">
+        <v>G</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>17</v>
+      </c>
+      <c r="B12" t="str">
+        <v>RN-2026-NM001-H</v>
+      </c>
+      <c r="C12" t="str">
+        <v>NM-001</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Nosač motora</v>
+      </c>
+      <c r="E12" t="str">
+        <v>50</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Kupac NM</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="I12" t="str">
+        <v>aktivan</v>
+      </c>
+      <c r="J12" t="str">
+        <v>PERA OPERATER</v>
+      </c>
+      <c r="K12" t="str">
+        <v>H</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>